--- a/site/Entra-ID-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>User Provisioning Settings</t>
+          <t>User Management Configuration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01KF2ST6Y7GH70E2MJCYT5X2DZ</t>
+          <t>h_01KW18GSEXVHXZYCA1AXESVYXP</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-ServiceNow-Integration-Guide/#01KF2ST6Y7GH70E2MJCYT5X2DZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-ServiceNow-Integration-Guide/#h_01KW18GSEXVHXZYCA1AXESVYXP</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>User Provisioning Threshold Settings</t>
+          <t>Manage Limit Configuration</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Create User Settings</t>
+          <t>Create Configuration</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Update User Settings</t>
+          <t>Update Configuration</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Group Management</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJEV1J5VWCA63R2SW4MGVXA3</t>
+          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-ServiceNow-Integration-Guide/#h_01KJEV1J5VWCA63R2SW4MGVXA3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-ServiceNow-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-ServiceNow-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-ServiceNow-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Offboarding</t>
+          <t>Group Management</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>h_01KJEV1J5VWCA63R2SW4MGVXA3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-ServiceNow-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-ServiceNow-Integration-Guide/#h_01KJEV1J5VWCA63R2SW4MGVXA3</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1051,6 +1051,28 @@
       <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Update the Integration to the Latest Version</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-ServiceNow-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
     </row>
